--- a/artfynd/A 10610-2023 artfynd.xlsx
+++ b/artfynd/A 10610-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10610-2023 artfynd.xlsx
+++ b/artfynd/A 10610-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95665176</v>
+        <v>95665227</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435181.7056443216</v>
+        <v>435664</v>
       </c>
       <c r="R2" t="n">
-        <v>6476798.484532882</v>
+        <v>6476516</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,19 +748,9 @@
           <t>2021-08-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-08-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95665182</v>
+        <v>95665176</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435285.8640114478</v>
+        <v>435181</v>
       </c>
       <c r="R3" t="n">
-        <v>6476846.001751248</v>
+        <v>6476799</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,19 +850,9 @@
           <t>2021-08-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,6 +877,108 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>95665182</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>skövde 5:77, Skövde, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>435286</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6476845</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-08-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-08-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10610-2023 artfynd.xlsx
+++ b/artfynd/A 10610-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -775,6 +780,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95665227</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95665176</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,8 +994,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95665182</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>